--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emretasci\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kale365-my.sharepoint.com/personal/emretasci_kale_com_tr/Documents/4. Gelişim Planı/Proje Portalı/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE6B70A-9B11-42B3-94D7-910658530805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1125" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C24CC567-8D42-419F-9E0D-5AF0A1E7BD06}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="560" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="560" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects Data" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="470">
   <si>
     <t>department order</t>
   </si>
@@ -99,10 +99,45 @@
     <t>Ürün ana veri yapısının incelenerek geliştirme/iyileştirme alanları ile hata ve/veya eksikliklerin tespit edilmesi ve bunların iyileştirilmesi, hataların giderilmesi faaliyetlerini içeren çalışmadır. Talep tahmin veri analitiği, SKU rasyonalizasyonu,  görünürlük, planlama stratejileri gibi pek çok çalışma için ürün ana veri yapısının iyileştirilmesi ihtiyacı ön koşul olarak bulunmaktadır.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ürün bilgilerinin ve karakteristik tanımlarının düzenli takibi ve kontrolü için power BI'da Ürün Dashboard çalışması tamamlanmıştır.
+Haftalık toplantılar ile ürün bilgilerindeki eksiklikler tespit edilmekte ve çalışmalar yapılmaktadır.
+Bölüm KPI'larına Ürün Ana Veri İyileştirme Endeksi eklenmiştir.
+</t>
+  </si>
+  <si>
+    <t>Piyasa kanalı tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+Kalite tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+Planlama stratejileri tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+DFU tanımları takip edilmekte ve eksiklikler giderilmektedir.
+Üretim kontrol notu takip edilmekte ve eksiklikler giderilmektedir.
+Ürün hiyerarşisi uyumsuzlukları tespit edilmekte ve düzeltilmektedir.
+Ürün hiyerarşisi tanımı yanlış olan kodlar tespit edilmekte ve düzeltilmektedir.
+Gömme rezervuar ürün grubunda set kodları ayrıştırılmıştır.
+Marka tanımları takip edilmekte ve eksiklikler giderilmektedir.
+Faturalama için ambalaj tipi tanımları takip edilmekte ve eksiklikler giderilmektedir.
+Orijin kodu bilgisinin düzenlenmesine yönelik çalışmalar devam etmektedir.
+SKM CTDA eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
+SKM Ebat eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
+SKM Kısa Kod eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
+Vitrifiye Renk tanımı eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
+Mükerrer açılan kodların tespiti ve düzenlenmesine yönelik çalışmalar devam etmektedir.</t>
+  </si>
+  <si>
     <t>Ürün Ambalaj Bilgilerinin Tanımlanması</t>
   </si>
   <si>
     <t>Ürün ana veri yapısında bulunan ambalaj bilgilerinin incelenerek hata ve/veya eksikliklerin tespit edilmesi ve bunların iyileştirilmesi, hataların giderilmesi faaliyetlerini içeren çalışmadır. Yükleme-rotalama optimizasyonu ve nakliye hesaplaması gibi pek çok çalışma için ürün ambalaj bilgilerinin tanımlanması ihtiyacı ön koşul olarak bulunmaktadır.</t>
+  </si>
+  <si>
+    <t>Vitrifiye ürün grubu için palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
+Vitrifiye ürün grubu için ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
+Mobilya ürün grubu için ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.</t>
+  </si>
+  <si>
+    <t>SKM ürün grubu için palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
+SKM ürün grubu için (numune kodlar) ürün ve palet kg bilgileri kontrol edilerek eksiklikler giderilecektir.
+Vitrifiye ürün grubu için ürün ve palet kg bilgileri kontrol edilerek eksiklikler giderilecektir.
+Vitrifiye ürün grubu için palet içi miktar bilgileri kontrol edilerek eksiklikler giderilecektir.</t>
   </si>
   <si>
     <t>Ürünler Arası İlişki Tanımlarının Oluşturulması</t>
@@ -132,9 +167,6 @@
     <t>KS2026-16</t>
   </si>
   <si>
-    <t>Başlamadı</t>
-  </si>
-  <si>
     <t>"Ürünler Arası İlişki Tanımlarının Oluşturulması" projesi kapsamında oluşturulan verinin kurumsal olarak saklanması ve yönetimi için yönetim aracı geliştirilmesi çalışmasıdır.</t>
   </si>
   <si>
@@ -251,6 +283,12 @@
   </si>
   <si>
     <t xml:space="preserve">Tahmin yetkinliğinin arttırılmasına yönelik olarak tahmin veri setinin değiştirilerek müşteri siparişi, fiyat, dış veriler, bayi satış verileri gibi bilgilerin kullanılarak yeni tahmin modelinin oluşturulmasına yönelik çalışmaları kapsamaktadır. </t>
+  </si>
+  <si>
+    <t>Tahmin modelinin ve uygulamanın oluşturulmasına yönelik proje adımları tamamlanmıştır.
+Veri setinin analizi ve yeni tahmin modelinin tasarımı oluşturulmuştur. (6 DFU)
+Modelin eğitimi tamamlanarak uygulama ile devreye alınmıştır.
+Tahmin sonuçları yıl sonuna kadar izlenecektir.</t>
   </si>
   <si>
     <t>Tahminde Müşteri, Kampanya, Teşhir Bilgilerinin Kullanımı</t>
@@ -345,10 +383,25 @@
     <t>Talep tahmin uygulamasının çıktısını kullanarak tedarik planlama adımına girdi olacak ve mutabakat sağlanmış talep değerlerinin oluşturulmasını sağlayacak talep zenginleştirme ve mutabakat uygulamasının geliştirilmesi çalışmasıdır. Tahmin sonuçlarının girdi olarak alınabildiği, belirli hiyerarşilerde düzeltme yapılabildiği, belirli kişilerin üzerinde çalışabildiği ve veri girişi yapabildiği esnek bir ortam geliştirme çalışmasıdır. Odoo platformu üzerinde In-house olarak geliştirilmektedir.</t>
   </si>
   <si>
+    <t xml:space="preserve">İstekler belirlenerek kavramsal tasarım dokümanı IT birimine iletilerek mutabakat sağlamıştır.
+İş akış dokümanı oluşturulmuştur.
+IT tarafından platform kararı verilmiştir.
+Proje planı ve backloglar oluşturulmuştur. (agile proje yönetimi)
+Toplam 8 sprint ile proje tamamlanmıştır.
+Sprint-1 kapsamında sistemsel düzenlemeler , sprint-2 kapsamında senaryo ve rollerin oluşturulması, excel ile verilerin yüklenmesi/raporlanması ve rol bazlı yetki düzenlemeleri yapılmıştır.
+Sprint-3 kapsamında DFU bazlı revizyonlar, katsayı ile revizyonlar ve iş akış durumunun gösterilmesi, sprint-4 kapsamında ise kullanıcı bazlı test ortamına erişim, iş akışının onaylanması ve yürütülmesi, değişiklik takibinin yapılması ve dönem bazlı kilitleme yapılmıştır.
+Sprint-5 ve sprint-6 kapsamında dönem bazlı kilitleme ve süreç onaylama/ilerleme adımları, tahmin karşılaştırmaları, piyasa bazında revizyonların yapılması ve yetkilendirme çalışmaları yürütülmüştür.
+Sprint-7 ve sprint-8 kapsamında raporlama ekranları, paralel ve sıralı çalışma modu, senaryo liste yönetimi ve revizyon geçmişi görüntüleme yapılmıştır.
+</t>
+  </si>
+  <si>
     <t>S&amp;OP Finansallaştırma Uyg. Geliştirilmesi</t>
   </si>
   <si>
     <t>KS2026-26</t>
+  </si>
+  <si>
+    <t>Başlamadı</t>
   </si>
   <si>
     <t>S&amp;OP süreci talep ve tedarik planlama adımlarından çıkan bilgilerin fiyat, maliyet, başta olmak üzere diğer finansal girdilerin kullanılarak tutarsal hale getirilmesi ve raporlanması çalışmasıdır. Buradan çıkan farklı senaryolar bazındaki finansalların değerlendirilmesi ile operasyonel planlara karar verilmesi sağlanacaktır. Bu çalışma In-house olarak planlanmaktadır.</t>
@@ -552,19 +605,19 @@
 OEM sipariş bazlı takip için standart veri yapısı oluşturuldu.</t>
   </si>
   <si>
-    <t>MTS Tip Ürünler İçin Max Stok Seviye Kontrol RPA</t>
+    <t>Stok Aşım Uyarı Sistemi Projesi</t>
   </si>
   <si>
     <t>30/11/2026</t>
   </si>
   <si>
-    <t>Üretim Planlama süreçlerinde MTS ürünlerin stok seviyeleri belirlenen maksimum stok limitlerinin üzerine çıkabilmektedir. Bu durum fazla üretim, gereksiz stok maliyeti, depo alanı kaybı ve işletme sermayesinin verimsiz kullanımına neden olmaktadır.. Bu proje kapsamında ERP sisteminden stok, üretim ve planlama verileri alınarak MTS ürünlerin güncel stok seviyeleri günlük olarak kontrol edilecektir. Geliştirilecek RPA robotu, ürün bazında tanımlı maksimum stok seviyeleri ile mevcut stok miktarlarını karşılaştıracak, limit aşımı olan ürünleri tespit edecek ve ilgili ekipleri otomatik olarak bilgilendirecektir.. RPA sayesinde manuel rapor kontrol süreçleri ortadan kaldırılarak erken aksiyon alınması, fazla üretimin önlenmesi ve stok seviyelerinin hedeflenen aralıkta tutulması amaçlanmaktadır.. Beklenen Kazanımlar. Maksimum stok aşımı tespit süresinde %90'a varan azalma. Manuel rapor hazırlama süresinde azalma. Fazla üretim kaynaklı stok maliyetlerinin düşürülmesi. Planlama kararlarının daha proaktif yönetilmesi. Stok devir hızının artırılması. Üretim ve depo kapasitesinin daha verimli kullanılması. Başarı Kriteri: Maksimum stok seviyesini aşan tüm MTS ürünlerin günlük olarak otomatik tespit edilmesi ve ilgili aksiyon sahiplerine zamanında bildirilmesi.</t>
-  </si>
-  <si>
-    <t>1. Süreç Analizi Mevcut stok kontrol süreci incelendi. Manuel takip edilen raporlar değerlendirildi. Maksimum stok takibi yapılan ürün grupları belirlendi. 2. Gereksinimlerin Belirlenmesi Kontrol edilecek veri kaynakları tanımlandı. ERP sisteminden çekilecek alanlar belirlendi. Malzeme kodu Malzeme açıklaması Mevcut stok miktarı Maksimum stok seviyesi Planlı üretim miktarı Açık sipariş miktarı 3. İş Kuralı Tasarımı Maksimum stok hesaplama mantığı oluşturuldu. Aşım kriterleri tanımlandı. Kritik eşik ve tolerans seviyeleri belirlendi. 4. RPA Tasarım Çalışması Veri çekme akışı tasarlandı. Kontrol algoritması oluşturuldu. Bildirim ve raporlama senaryoları belirlendi.</t>
-  </si>
-  <si>
-    <t>1. ERP Veri Entegrasyonunun Tamamlanması ERP sisteminden otomatik veri çekilmesi. Veri doğrulama kontrollerinin eklenmesi. 2. RPA Geliştirme Çalışmaları Günlük tetikleme mekanizmasının kurulması. Ürün bazında stok kontrol modülünün geliştirilmesi. Stok aşımı hesaplama algoritmasının entegrasyonu. 3. Otomatik Bildirim Yapısının Kurulması Kritik ürünlerin e-posta ile bildirilmesi. Planlama ekibine günlük özet rapor gönderilmesi. Bölüm yöneticilerine haftalık durum raporu oluşturulması. 4. Dashboard ve Raporlama Aşım yaşanan ürün listesinin oluşturulması. Ürün bazında stok trendlerinin görüntülenmesi. Aksiyon takibi için KPI ekranlarının hazırlanması. 5. Test ve Doğrulama Pilot ürün grubu üzerinde test yapılması. Sonuçların manuel kontroller ile karşılaştırılması. Hata senaryolarının doğrulanması. 6. Canlı Kullanıma Geçiş RPA'nın üretim ortamına alınması. Kullanıcı eğitimlerinin tamamlanması. Performans takibinin başlatılması.</t>
+    <t>Üretim Planlama süreçlerinde tüm ürünlerin stok seviyeleri belirlenen maksimum stok limitlerinin üzerine çıkabilmektedir. Bu durum fazla üretim, gereksiz stok maliyeti, depo alanı kaybı ve işletme sermayesinin verimsiz kullanımına neden olmaktadır.. Bu proje kapsamında ERP sisteminden stok, üretim ve planlama verileri alınarak tüm ürünlerin güncel stok seviyeleri günlük olarak kontrol edilecektir. Geliştirilecek sistem, ürün bazında tanımlı maksimum stok seviyeleri ile mevcut stok miktarlarını karşılaştıracak, limit aşımı olan ürünleri tespit edecek ve ilgili ekipleri otomatik olarak bilgilendirecektir. Oluşturulacak bu sistem sayesinde manuel rapor kontrol süreçleri ortadan kaldırılarak erken aksiyon alınması, fazla üretimin önlenmesi ve stok seviyelerinin hedeflenen aralıkta tutulması amaçlanmaktadır.. Beklenen Kazanımlar. Maksimum stok aşımı tespit süresinde %90'a varan azalma. Manuel rapor hazırlama süresinde azalma. Fazla üretim kaynaklı stok maliyetlerinin düşürülmesi. Planlama kararlarının daha proaktif yönetilmesi. Stok devir hızının artırılması. Üretim ve depo kapasitesinin daha verimli kullanılması. Başarı Kriteri: Maksimum stok seviyesini aşan tüm ürünlerin günlük olarak otomatik tespit edilmesi ve ilgili aksiyon sahiplerine zamanında bildirilmesi.</t>
+  </si>
+  <si>
+    <t>1. Süreç Analizi Mevcut stok kontrol süreci incelendi. Manuel takip edilen raporlar değerlendirildi. Maksimum stok takibi yapılan ürün grupları belirlendi. 2. Gereksinimlerin Belirlenmesi Kontrol edilecek veri kaynakları tanımlandı. ERP sisteminden çekilecek alanlar belirlendi. Malzeme kodu Malzeme açıklaması Mevcut stok miktarı Maksimum stok seviyesi Planlı üretim miktarı Açık sipariş miktarı 3. İş Kuralı Tasarımı Maksimum stok hesaplama mantığı oluşturuldu. Aşım kriterleri tanımlandı. Kritik eşik ve tolerans seviyeleri belirlendi. 4. Sistem Tasarım Çalışması Veri çekme akışı tasarlandı. Kontrol algoritması oluşturuldu. Bildirim ve raporlama senaryoları belirlendi.</t>
+  </si>
+  <si>
+    <t>1. ERP Veri Entegrasyonunun Tamamlanması ERP sisteminden otomatik veri çekilmesi. Veri doğrulama kontrollerinin eklenmesi. 2. Sistem Geliştirme Çalışmaları Günlük tetikleme mekanizmasının kurulması. Ürün bazında stok kontrol modülünün geliştirilmesi. Stok aşımı hesaplama algoritmasının entegrasyonu. 3. Otomatik Bildirim Yapısının Kurulması Kritik ürünlerin e-posta ile bildirilmesi. Planlama ekibine günlük özet rapor gönderilmesi. Bölüm yöneticilerine haftalık durum raporu oluşturulması. 4. Dashboard ve Raporlama Aşım yaşanan ürün listesinin oluşturulması. Ürün bazında stok trendlerinin görüntülenmesi. Aksiyon takibi için KPI ekranlarının hazırlanması. 5. Test ve Doğrulama Pilot ürün grubu üzerinde test yapılması. Sonuçların manuel kontroller ile karşılaştırılması. Hata senaryolarının doğrulanması. 6. Canlı Kullanıma Geçiş sisteminin üretim ortamına alınması. Kullanıcı eğitimlerinin tamamlanması. Performans takibinin başlatılması.</t>
   </si>
   <si>
     <t>TZY Planlama Power BI Dashboard</t>
@@ -718,15 +771,14 @@
 </t>
   </si>
   <si>
-    <t>KS01 &amp; KS02 kapsamında emniyet stoğu tanımlanan SKU oranının artırılması ve uygulamanın daha geniş malzeme gruplarına yaygınlaştırılması.
+    <t xml:space="preserve">KS01 &amp; KS02 kapsamında emniyet stoğu tanımlanan SKU oranının artırılması ve uygulamanın daha geniş malzeme gruplarına yaygınlaştırılması.
 Dinamik emniyet stoğu ve min–max yönetim yapısının standartlaştırılarak sistemsel hale getirilmesi.
 Belirlenen öncelikli malzeme gruplarında yapılan analizler doğrultusunda MRP parametrelerinin ve ihtiyaç oluşturma yapısının iyileştirilmesi.
 MRP sinyal kalitesini artırmak amacıyla tüketim frekansı, geçmiş tüketim, stok seviyesi ve ihtiyaç yapısının daha etkin şekilde sisteme dahil edilmesi.
 Stok tutarı ile tüketim ilişkisine göre optimum stok / yeterlilik seviyelerinin malzeme grubu bazında belirlenmesi.
 Ürün ağaçlarının haftalık olarak otomatik mail ile paylaşılmasına yönelik SAP-Mail yapısının devreye alınması.
-Satınalma, Üretim Planlama ve Depo süreçleri arasındaki bilgi akışının hızlandırılması ve sürdürülebilir bir takip mekanizmasının oluşturulması.
 MRP, stok, açık sipariş ve üretim planı bilgilerinin mümkün olduğunca tek bir izleme ve karar destek yapısında birleştirilmesi.
-MRP iyileştirmelerinin etkisinin; stok seviyesi, stok devir hızı, 180+ stok, açık SAT/SAS ve hizmet seviyesi KPI’ları üzerinden düzenli olarak ölçülmesi.</t>
+</t>
   </si>
   <si>
     <t>SAP QM Kapsamında SKT Uyarı ve FIFO Kontrol Projesi</t>
@@ -784,10 +836,8 @@
 İş Güvenliği ve Depo Düzeni İyileştirmeleri tamamlanmıştır.
 Eğitim, Dokümantasyon ve Standartlaştırma tamamlanmıştır.
 Pilot Uygulama ve Yaygınlaştırma devam etmektedir.
-KPI Takibi ve Süreç Stabilizasyonu devam etmektedir.</t>
-  </si>
-  <si>
-    <t>Ambalaj malzemeleri için mevcut fiziksel depolama alanı yetersiz kalmaktadır. Artan hacim ve çeşitlilik dikkate alınarak, daha verimli yerleşim ve ilave alan ihtiyacının değerlendirilmesine ihtiyaç vardır.
+KPI Takibi ve Süreç Stabilizasyonu devam etmektedir.
+Ambalaj malzemeleri için mevcut fiziksel depolama alanı yetersiz kalmaktadır. Artan hacim ve çeşitlilik dikkate alınarak, daha verimli yerleşim ve ilave alan ihtiyacının değerlendirilmesine ihtiyaç vardır.
 KPI Set;  Stok doğruluğu, Malzeme bulunurluk,Hat besleme, Yetersizlik, 180+% , Adresleme şeklinde yapılandırılmaya çalışılıyor.</t>
   </si>
   <si>
@@ -799,7 +849,7 @@
   </si>
   <si>
     <t>Power BI 180+ yaşlı stoklara ait düzenli yaş analiz raporları oluşturulmuş ve aylık takip yapısı devreye alınmıştır.
-Malzeme bazlı son tüketim, son satın alma ve hareket analizleri için SAP 'de Stok Etkinlik Raporu tasarlanmıştır.
+Malzeme bazlı son tüketim, son satın alma ve hareket analizleri için SAP 'de Stok Etkinlik Raporu tasarlanmıştır ve ilgililerle(üretim/bakım/satınalma dep.) paylaşılmıştır.
 Kullanımı olmayan ve düşük hareketli malzemeler için aksiyon takip listeleri oluşturulmuştur.
 Açık SAT ve SAS süreçleri analiz edilerek geçmiş tarihli kayıtların kapatılması için takip mekanizması kurulmuştur.
 Emniyet stokları belirli malzeme grupları için tanımlanmış ve düzenli takip edilmeye başlanmıştır.
@@ -809,10 +859,8 @@
 ABC &amp; XYZ analizleri revize edilerek stok önceliklendirme yapısı güncellenmiştir.
 Düşük hareketli ve atıl stoklar için aksiyon yönetim sürecinin standardize edilmiştir.
 Açık SAT ve SAS süreçleri için otomatik takip ve uyarı mekanizmasının geliştirilmiştir.
-Yaşlı stoklar için satış, iade ve bertaraf süreçlerinin hızlandırılmıştır. Akrilik yarı mamullerin bertaraf edilmesi konusu ile ilgili gereken aksiyon alınmıştır.</t>
-  </si>
-  <si>
-    <t>Satın alma süreçlerinde ihtiyaç fazlası stok oluşumunu önleyecek kontrol yapılarının geliştirilmesi
+Yaşlı stoklar için satış, iade ve bertaraf süreçlerinin hızlandırılmıştır. Akrilik yarı mamullerin bertaraf edilmesi konusu ile ilgili gereken aksiyon alınmıştır.
+Satın alma süreçlerinde ihtiyaç fazlası stok oluşumunu önleyecek kontrol yapılarının geliştirilmesi
 Depo ve planlama ekipleri için stok verimliliği odaklı süreç eğitimlerinin gerçekleştirilmesi.</t>
   </si>
   <si>
@@ -862,13 +910,11 @@
 Mükerrer ve benzer malzeme kodları ana veri seviyesinde gözden geçirilerek birleştirilecektir. Tüm malzeme kodları henüz tamamlanmamıştır.
 Yeni malzeme kodu açılış süreci belirli kurallar ve onay mekanizması ile kontrollü hale getirilmiştir.
 Tüm operasyonda kullanılmak üzere standart bir kod isimlendirme yapısı oluşturulmuştur.
-</t>
-  </si>
-  <si>
-    <t>Görsel arşiv (SKUMATCH) ile malzeme ana veri süreci entegre edilerek doğru kod seçimi desteklenecektir
+Görsel arşiv (SKUMATCH) ile malzeme ana veri süreci entegre edilerek doğru kod seçimi desteklenecektir
 Malzeme ana veri kalitesi belirli KPI’lar ile düzenli olarak izlenecek ve raporlanacaktır
 Kod talep süreçlerinin standart hale getirilmesi için prosedür/talimat dokümanının hazırlanarak devreye alınacaktır.
-Kod talep yönetiminin SAP tarafına alınması ile ilgili IT talep hızlandırılmaya çalışılacak.</t>
+Kod talep yönetiminin SAP tarafına alınması ile ilgili IT talep hızlandırılmaya çalışılacak.
+</t>
   </si>
   <si>
     <t>Lojistik</t>
@@ -897,20 +943,12 @@
 Kale SAP sistemindeki GTIP bilgilerinin kontrol edildi. Eksiklikler tamamlandı.
 GTİP akışları karşılıklı olarak test edildi.
 İthalat Süreci Kavramsal çalışması tamamlandı.
-MM03’teki GTIP tanımlarının girişi tamamlandı.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-VPN Bağlantı ve KEQ sistemine kullanıcı bağlantı. (Merkezi gümrükleme uçtan uca ihracat-ithalat süreci için)
-Geliştirme adımı, kavramsal onayı sonrası, geliştirme yönlendirmesi Kale tarafından yapıldıktan sonra başlayacak.
-OGİ İşlemler Menusü, kullanım dokumanı gibi, SAP'deki kurgunun kullanıcı dokumanı hazırlanacak.
-SAP’te VL31N ile oluşturulan Alınan Teslimatların, gümrük sistemine otomatik olarak aktarılması
-*Her bir Alınan Teslimat kaydı, gümrük tarafında ayrı bir dosya olarak ele alınacaktır.
-Gümrük sistemi üzerindeki statü bilgilerinin, SAP’ye geri akması
-*Bu bilgilerin, SAP tarafında Alınan Teslimat başlık ekranındaki “İthalat – İrsaliye” sekmesine güncellenmesi beklenmektedir.
-SAP’te ZMMR0029 işlem kodu ile oluşturulan ödeme emrine ait,
-*Bankadan dönen ödeme gerçekleşme bilgisinin, SAP üzerinden gümrük sistemine iletilmesi.
-</t>
+MM03’teki GTIP tanımlarının girişi tamamlandı.
+İthalata konu malzeme kodları gtipleri sistemde tanımlandı.
+İthalat Beyannamede hata düzeltme kullanıcı dokümanı hazırlandı
+İthalat Kokpiti kullanıcı dokümanı hazırlandı
+İthalat mail yönetimi kullanıcı dokümanı hazırlandı
+İthalat Entegrasyonu canlıya alındı.</t>
   </si>
   <si>
     <t>Outbound  Lojistik</t>
@@ -939,7 +977,8 @@
     <t>Risk Kontrol Müdürlüğü tarafından teminat yapısı ile ilgili ayrı bir rapor çalışılıyor. Henüz TZY çalışmaya dahil edilmedi.
 Teminat konusunun çalışılması ve olası çözümlerin değerlendirilmesi​
 Sevk istemiyor, depo doluluğu, v.b. bayi kaynaklı sebeplerin genel bir BOD yaklaşımı ile sevkiyatının yapılması​
-Rota ve araç doluluğu kaynaklı beklemelerin belirli kural ve sürelere bağlanıp, bu süreler sonucunda belirlenmiş aksiyonların yürütülmesi</t>
+Rota ve araç doluluğu kaynaklı beklemelerin belirli kural ve sürelere bağlanıp, bu süreler sonucunda belirlenmiş aksiyonların yürütülmesi
+Risk Kontrol Müdürlüğünün çalışması tamamlanmadığı için proje askıya alındı.</t>
   </si>
   <si>
     <t>Sipariş Kurallarının Güncellenmesi</t>
@@ -984,10 +1023,13 @@
 Tırport ile Cube IQ denemeleri yapıldı. Simülasyonun sunumu ve sonuçlarının değerlendirildi. Verimsiz olduğu gözlendi. SAP entegrasyonu bulunmuyor.		
 MD Group saha ziyareti ve işlem listesi görüşmesi yapıldı.
 Kaleseramik – TM Optimizer Projesi Analiz raporu paylaşıldı.
-Optiyol yükleme ve rota planlama çalışması yapıldı.</t>
-  </si>
-  <si>
-    <t>MDP ile palet, paket dönüşümüne çözüm alternatifleri için geri bildirim yapıldı. Dönüş bekleniyor.
+Optiyol yükleme ve rota planlama çalışması yapıldı.
+Optiyol rota optimizsyonu çalışmaları yapıldı. Çalışmalrın sunumu tarafımıza yapıldı görülen aksaklıkların düzeltilmesi için geri bildirim yapıldı. Düzeltmeler yapıldı. Kontrol edildi.
+Golive yükleme ve rota optimizasyonu son araşamaya gelindi ve sunumu yapıldı.</t>
+  </si>
+  <si>
+    <r>
+      <t>MDP ile palet, paket dönüşümüne çözüm alternatifleri için geri bildirim yapıldı. Dönüş bekleniyor.
 MDP Vitra benchmark için geri bildirim bekleniyor.
 Optiyol sadece rota optimizasyonu desteği verdiğinden mevcut durumda askıya alındı.
 Kuralların tanımlanacak:
@@ -1015,9 +1057,30 @@
 TM’ye gönderme (SV) adımının manuel olmaktan çıkarılacak (RPA / otomasyon)
 Optimizasyon havuzunun genişletilecek.
 Operasyonel karar noktalarının gözden geçirilmesi:
-Teslimat oluşturma aşamasında verilen kararların optimizasyonu kısıtlayıp kısıtlamadığı değerlendirilecek.
+Teslimat oluşturma aşamasında verilen kararların optimizasyonu kısıtlayıp kısıtlamadığı değerlendirilecek.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Optiyol yükleme optimizasyonu geliştirmesi bekleniyor.
+Golive yükleme ve rota optimizasyonu tamamlandı. Tarafımızca kontrol edilip, görülen eksik ve hatalar bildirilecek.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
 Uyarı / ikaz sistemi kurgusu:
 YZ Yanımda projesi kapsamında sapma, doluluk, bekleme süresi gibi konularda uyarı mekanizmaları tasarlanacak.</t>
+    </r>
   </si>
   <si>
     <t>Kalite Belgesi</t>
@@ -1041,10 +1104,7 @@
 Sistem kurulumu ve uygulanmas için alınacak aksiyonlar belirlendi.
 Bağlam ve İlgili Taraflar Analizi 16 Nisan'da başladı. Belgelendirme firması yönlendirmesi ile haftalık güncellemeler yapılıyor.
 22 Mayıs tarihinde el kitabı ve ek dokümanlar hazırlandı.
-4 Haziran'da nihai kontroller yapılarak belgelendirme ay sonuna kadar tamamlanacak.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
+4 Haziran'da nihai kontroller yapılarak belgelendirme ay sonuna kadar tamamlanacak.
 Kalite standartlarına uyum adına belgelerde güncelleme yapılacak.
 Yerinde denetim yapılacak.
 Belgenin alınması.</t>
@@ -2402,59 +2462,6 @@
 Müşteri deneyimini iyileştirmek
 Kategori Pazarlama tarafından yürütülen ürün yönetimi sürecine girdi ve öneriler sağlamak. (nihai müşteri talepleri)</t>
   </si>
-  <si>
-    <t xml:space="preserve">Ürün bilgilerinin ve karakteristik tanımlarının düzenli takibi ve kontrolü için power BI'da Ürün Dashboard çalışması tamamlanmıştır.
-Haftalık toplantılar ile ürün bilgilerindeki eksiklikler tespit edilmekte ve çalışmalar yapılmaktadır.
-Bölüm KPI'larına Ürün Ana Veri İyileştirme Endeksi eklenmiştir.
-</t>
-  </si>
-  <si>
-    <t>Piyasa kanalı tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
-Kalite tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
-Planlama stratejileri tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
-DFU tanımları takip edilmekte ve eksiklikler giderilmektedir.
-Üretim kontrol notu takip edilmekte ve eksiklikler giderilmektedir.
-Ürün hiyerarşisi uyumsuzlukları tespit edilmekte ve düzeltilmektedir.
-Ürün hiyerarşisi tanımı yanlış olan kodlar tespit edilmekte ve düzeltilmektedir.
-Gömme rezervuar ürün grubunda set kodları ayrıştırılmıştır.
-Marka tanımları takip edilmekte ve eksiklikler giderilmektedir.
-Faturalama için ambalaj tipi tanımları takip edilmekte ve eksiklikler giderilmektedir.
-Orijin kodu bilgisinin düzenlenmesine yönelik çalışmalar devam etmektedir.
-SKM CTDA eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
-SKM Ebat eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
-SKM Kısa Kod eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
-Vitrifiye Renk tanımı eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
-Mükerrer açılan kodların tespiti ve düzenlenmesine yönelik çalışmalar devam etmektedir.</t>
-  </si>
-  <si>
-    <t>Vitrifiye ürün grubu için palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
-Vitrifiye ürün grubu için ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
-Mobilya ürün grubu için ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.</t>
-  </si>
-  <si>
-    <t>SKM ürün grubu için palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
-SKM ürün grubu için (numune kodlar) ürün ve palet kg bilgileri kontrol edilerek eksiklikler giderilecektir.
-Vitrifiye ürün grubu için ürün ve palet kg bilgileri kontrol edilerek eksiklikler giderilecektir.
-Vitrifiye ürün grubu için palet içi miktar bilgileri kontrol edilerek eksiklikler giderilecektir.</t>
-  </si>
-  <si>
-    <t>Tahmin modelinin ve uygulamanın oluşturulmasına yönelik proje adımları tamamlanmıştır.
-Veri setinin analizi ve yeni tahmin modelinin tasarımı oluşturulmuştur. (6 DFU)
-Modelin eğitimi tamamlanarak uygulama ile devreye alınmıştır.
-Tahmin sonuçları yıl sonuna kadar izlenecektir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">İstekler belirlenerek kavramsal tasarım dokümanı IT birimine iletilerek mutabakat sağlamıştır.
-İş akış dokümanı oluşturulmuştur.
-IT tarafından platform kararı verilmiştir.
-Proje planı ve backloglar oluşturulmuştur. (agile proje yönetimi)
-Toplam 8 sprint ile proje tamamlanmıştır.
-Sprint-1 kapsamında sistemsel düzenlemeler , sprint-2 kapsamında senaryo ve rollerin oluşturulması, excel ile verilerin yüklenmesi/raporlanması ve rol bazlı yetki düzenlemeleri yapılmıştır.
-Sprint-3 kapsamında DFU bazlı revizyonlar, katsayı ile revizyonlar ve iş akış durumunun gösterilmesi, sprint-4 kapsamında ise kullanıcı bazlı test ortamına erişim, iş akışının onaylanması ve yürütülmesi, değişiklik takibinin yapılması ve dönem bazlı kilitleme yapılmıştır.
-Sprint-5 ve sprint-6 kapsamında dönem bazlı kilitleme ve süreç onaylama/ilerleme adımları, tahmin karşılaştırmaları, piyasa bazında revizyonların yapılması ve yetkilendirme çalışmaları yürütülmüştür.
-Sprint-7 ve sprint-8 kapsamında raporlama ekranları, paralel ve sıralı çalışma modu, senaryo liste yönetimi ve revizyon geçmişi görüntüleme yapılmıştır.
-</t>
-  </si>
 </sst>
 </file>
 
@@ -2463,7 +2470,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2544,6 +2551,17 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2572,7 +2590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2648,6 +2666,12 @@
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2993,27 +3017,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M111"/>
-  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="6.3125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12.3125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.3125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="18.89453125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="15.1015625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.3125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="11" customWidth="1"/>
     <col min="7" max="7" width="10" style="11" customWidth="1"/>
-    <col min="8" max="8" width="11.1015625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="11.3125" style="14" customWidth="1"/>
-    <col min="10" max="10" width="12.41796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="71.3125" style="11" customWidth="1"/>
-    <col min="12" max="12" width="70.89453125" style="11" customWidth="1"/>
-    <col min="13" max="13" width="75.7890625" style="13" customWidth="1"/>
-    <col min="14" max="14" width="8.89453125" style="12" customWidth="1"/>
-    <col min="15" max="16384" width="8.89453125" style="12"/>
+    <col min="8" max="8" width="11.140625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" style="14" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="71.28515625" style="11" customWidth="1"/>
+    <col min="12" max="12" width="70.85546875" style="11" customWidth="1"/>
+    <col min="13" max="13" width="75.7109375" style="13" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="12" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" s="7" customFormat="1" ht="57.6">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3054,7 +3079,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="259.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" ht="288" hidden="1">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -3087,13 +3112,13 @@
         <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>469</v>
+        <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="111" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="111" hidden="1" customHeight="1">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -3110,7 +3135,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="10">
@@ -3123,16 +3148,16 @@
         <v>17</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>471</v>
+        <v>23</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="115.15" hidden="1">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -3149,7 +3174,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="10">
@@ -3162,16 +3187,16 @@
         <v>17</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="43.15" hidden="1" customHeight="1">
       <c r="A5" s="8">
         <v>1</v>
       </c>
@@ -3188,10 +3213,10 @@
         <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H5" s="10">
         <v>46204</v>
@@ -3203,14 +3228,14 @@
         <v>17</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="72" hidden="1">
       <c r="A6" s="8">
         <v>1</v>
       </c>
@@ -3224,23 +3249,23 @@
         <v>14</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13" ht="43.15" hidden="1">
       <c r="A7" s="8">
         <v>1</v>
       </c>
@@ -3254,23 +3279,23 @@
         <v>14</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L7" s="13"/>
     </row>
-    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13" ht="43.15" hidden="1">
       <c r="A8" s="8">
         <v>1</v>
       </c>
@@ -3284,23 +3309,23 @@
         <v>14</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L8" s="13"/>
     </row>
-    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13" ht="43.15" hidden="1">
       <c r="A9" s="8">
         <v>1</v>
       </c>
@@ -3314,23 +3339,23 @@
         <v>14</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
       <c r="J9" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L9" s="13"/>
     </row>
-    <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13" ht="43.15" hidden="1">
       <c r="A10" s="8">
         <v>1</v>
       </c>
@@ -3344,25 +3369,25 @@
         <v>14</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13" ht="43.15" hidden="1">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -3376,25 +3401,25 @@
         <v>14</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L11" s="13"/>
     </row>
-    <row r="12" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13" ht="100.9" hidden="1">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -3405,13 +3430,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="10">
@@ -3421,19 +3446,19 @@
         <v>45930</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="115.15" hidden="1">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -3444,13 +3469,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="10">
@@ -3460,17 +3485,17 @@
         <v>46022</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13" ht="72" hidden="1">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -3481,13 +3506,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="10">
@@ -3497,17 +3522,17 @@
         <v>46234</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>473</v>
+        <v>65</v>
       </c>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13" ht="57.6" hidden="1">
       <c r="A15" s="8">
         <v>1</v>
       </c>
@@ -3518,28 +3543,28 @@
         <v>2</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
       <c r="J15" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L15" s="13"/>
     </row>
-    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" ht="43.15" hidden="1">
       <c r="A16" s="8">
         <v>1</v>
       </c>
@@ -3550,28 +3575,28 @@
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L16" s="13"/>
     </row>
-    <row r="17" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:13" ht="129.6" hidden="1">
       <c r="A17" s="8">
         <v>1</v>
       </c>
@@ -3582,13 +3607,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="10">
@@ -3598,17 +3623,17 @@
         <v>46112</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:13" ht="129.6" hidden="1">
       <c r="A18" s="8">
         <v>1</v>
       </c>
@@ -3619,13 +3644,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="10">
@@ -3638,16 +3663,16 @@
         <v>17</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="72" hidden="1">
       <c r="A19" s="8">
         <v>1</v>
       </c>
@@ -3658,13 +3683,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="10">
@@ -3674,19 +3699,19 @@
         <v>46112</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="273.60000000000002" hidden="1">
       <c r="A20" s="8">
         <v>1</v>
       </c>
@@ -3697,16 +3722,16 @@
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H20" s="10">
         <v>46023</v>
@@ -3715,17 +3740,17 @@
         <v>46234</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>474</v>
+        <v>90</v>
       </c>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:13" ht="72" hidden="1">
       <c r="A21" s="8">
         <v>1</v>
       </c>
@@ -3736,16 +3761,16 @@
         <v>3</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H21" s="10">
         <v>46174</v>
@@ -3754,14 +3779,14 @@
         <v>46295</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L21" s="13"/>
     </row>
-    <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:13" ht="43.15" hidden="1">
       <c r="A22" s="8">
         <v>1</v>
       </c>
@@ -3772,13 +3797,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="10">
@@ -3788,14 +3813,14 @@
         <v>46295</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:13" ht="72" hidden="1">
       <c r="A23" s="8">
         <v>1</v>
       </c>
@@ -3806,16 +3831,16 @@
         <v>3</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H23" s="10">
         <v>46327</v>
@@ -3824,14 +3849,14 @@
         <v>46387</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L23" s="13"/>
     </row>
-    <row r="24" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:13" ht="100.9" hidden="1">
       <c r="A24" s="8">
         <v>1</v>
       </c>
@@ -3842,13 +3867,13 @@
         <v>4</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="10">
@@ -3858,19 +3883,19 @@
         <v>46112</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="43.15" hidden="1">
       <c r="A25" s="8">
         <v>1</v>
       </c>
@@ -3881,13 +3906,13 @@
         <v>4</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="10">
@@ -3897,17 +3922,17 @@
         <v>46203</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="43.15" hidden="1">
       <c r="A26" s="8">
         <v>1</v>
       </c>
@@ -3918,13 +3943,13 @@
         <v>4</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="10">
@@ -3934,34 +3959,34 @@
         <v>46265</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="144" hidden="1">
       <c r="A27" s="8">
         <v>2</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C27" s="8">
         <v>1</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="10">
@@ -3971,33 +3996,33 @@
         <v>46112</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="115.15" hidden="1">
       <c r="A28" s="8">
         <v>2</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C28" s="8">
         <v>1</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="10">
@@ -4007,101 +4032,101 @@
         <v>46203</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M28" s="11"/>
     </row>
-    <row r="29" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:13" ht="43.15" hidden="1">
       <c r="A29" s="8">
         <v>2</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C29" s="8">
         <v>1</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
       <c r="J29" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L29" s="13"/>
     </row>
-    <row r="30" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:13" ht="43.15" hidden="1">
       <c r="A30" s="8">
         <v>2</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C30" s="8">
         <v>1</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
       <c r="J30" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="L30" s="13"/>
     </row>
-    <row r="31" spans="1:13" ht="259.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:13" ht="318" hidden="1">
       <c r="A31" s="8">
         <v>2</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C31" s="8">
         <v>1</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="H31" s="10">
         <v>46174</v>
@@ -4110,33 +4135,33 @@
         <v>46356</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="M31" s="15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="144" hidden="1">
       <c r="A32" s="8">
         <v>2</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C32" s="8">
         <v>1</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="10">
@@ -4146,36 +4171,36 @@
         <v>46356</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M32" s="15" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="86.45" hidden="1">
       <c r="A33" s="8">
         <v>2</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C33" s="8">
         <v>1</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="10">
@@ -4185,34 +4210,34 @@
         <v>46356</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:13" ht="144" hidden="1">
       <c r="A34" s="8">
         <v>2</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C34" s="8">
         <v>1</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="10">
@@ -4222,75 +4247,75 @@
         <v>46356</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="M34" s="15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="216" x14ac:dyDescent="0.55000000000000004">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="231" hidden="1">
       <c r="A35" s="8">
         <v>2</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C35" s="8">
         <v>1</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="10">
         <v>46266</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M35" s="15" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="187.15" hidden="1">
       <c r="A36" s="8">
         <v>2</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C36" s="8">
         <v>1</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="10">
@@ -4303,36 +4328,36 @@
         <v>17</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="M36" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="86.45" hidden="1">
       <c r="A37" s="8">
         <v>2</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C37" s="8">
         <v>2</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H37" s="10">
         <v>45839</v>
@@ -4341,68 +4366,68 @@
         <v>46112</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="43.15" hidden="1">
       <c r="A38" s="8">
         <v>2</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C38" s="8">
         <v>2</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L38" s="13"/>
     </row>
-    <row r="39" spans="1:13" ht="374.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:13" ht="388.9" hidden="1">
       <c r="A39" s="8">
         <v>2</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C39" s="8">
         <v>2</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H39" s="10">
         <v>46023</v>
@@ -4411,34 +4436,34 @@
         <v>46203</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="M39" s="11"/>
     </row>
-    <row r="40" spans="1:13" ht="374.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:13" ht="374.45" hidden="1">
       <c r="A40" s="8">
         <v>2</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C40" s="8">
         <v>2</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G40" s="13"/>
       <c r="H40" s="10">
@@ -4448,36 +4473,36 @@
         <v>46295</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="158.44999999999999" hidden="1">
       <c r="A41" s="8">
         <v>2</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C41" s="8">
         <v>2</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="G41" s="13"/>
       <c r="H41" s="10">
@@ -4487,34 +4512,34 @@
         <v>46192</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="M41" s="11"/>
     </row>
-    <row r="42" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:13" ht="144" hidden="1">
       <c r="A42" s="8">
         <v>2</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C42" s="8">
         <v>2</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G42" s="13"/>
       <c r="H42" s="10">
@@ -4524,73 +4549,73 @@
         <v>46174</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M42" s="11"/>
     </row>
-    <row r="43" spans="1:13" ht="360" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:13" ht="361.5" hidden="1">
       <c r="A43" s="8">
         <v>2</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C43" s="8">
         <v>2</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="10">
         <v>45870</v>
       </c>
       <c r="I43" s="10">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="M43" s="17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+        <v>174</v>
+      </c>
+      <c r="M43" s="26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="201.6" hidden="1">
       <c r="A44" s="8">
         <v>2</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C44" s="8">
         <v>2</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="10">
@@ -4603,111 +4628,107 @@
         <v>17</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L44" s="16" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="M44" s="17" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="216" x14ac:dyDescent="0.55000000000000004">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="303.75" hidden="1">
       <c r="A45" s="8">
         <v>2</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C45" s="8">
         <v>3</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="10">
         <v>46023</v>
       </c>
       <c r="I45" s="10">
-        <v>46265</v>
+        <v>46387</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="M45" s="15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="259.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>184</v>
+      </c>
+      <c r="M45" s="15"/>
+    </row>
+    <row r="46" spans="1:13" ht="259.5" hidden="1" customHeight="1">
       <c r="A46" s="8">
         <v>2</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C46" s="8">
         <v>3</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="10">
         <v>46023</v>
       </c>
       <c r="I46" s="10">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="M46" s="15" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="316.8" x14ac:dyDescent="0.55000000000000004">
+        <v>187</v>
+      </c>
+      <c r="M46" s="15"/>
+    </row>
+    <row r="47" spans="1:13" ht="318" hidden="1">
       <c r="A47" s="8">
         <v>2</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C47" s="8">
         <v>2</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="10">
@@ -4720,111 +4741,109 @@
         <v>17</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="M47" s="15" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="332.25" hidden="1">
       <c r="A48" s="8">
         <v>2</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C48" s="8">
         <v>2</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="10">
         <v>46023</v>
       </c>
       <c r="I48" s="10">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="M48" s="15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="230.4" x14ac:dyDescent="0.55000000000000004">
+        <v>194</v>
+      </c>
+      <c r="M48" s="15"/>
+    </row>
+    <row r="49" spans="1:13" ht="245.25">
       <c r="A49" s="8">
         <v>3</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C49" s="8">
         <v>1</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="10">
         <v>45839</v>
       </c>
       <c r="I49" s="10">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M49" s="18" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="174">
       <c r="A50" s="8">
         <v>3</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C50" s="8">
         <v>2</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="10">
@@ -4834,75 +4853,75 @@
         <v>46203</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L50" s="15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M50" s="11" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="57.75">
       <c r="A51" s="8">
         <v>3</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C51" s="8">
         <v>2</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="10">
         <v>46113</v>
       </c>
       <c r="I51" s="10">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="115.15">
       <c r="A52" s="8">
         <v>3</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C52" s="8">
         <v>2</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="10">
@@ -4912,114 +4931,112 @@
         <v>46022</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M52" s="11"/>
     </row>
-    <row r="53" spans="1:13" ht="409.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:13" ht="409.6">
       <c r="A53" s="8">
         <v>3</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C53" s="8">
         <v>2</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H53" s="10">
         <v>45778</v>
       </c>
       <c r="I53" s="10">
-        <v>46265</v>
+        <v>46387</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="M53" s="11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+        <v>217</v>
+      </c>
+      <c r="M53" s="27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="231">
       <c r="A54" s="8">
         <v>3</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C54" s="8">
         <v>3</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="10">
         <v>45992</v>
       </c>
       <c r="I54" s="10">
-        <v>46203</v>
+        <v>46269</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="M54" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>223</v>
+      </c>
+      <c r="M54" s="11"/>
+    </row>
+    <row r="55" spans="1:13" ht="86.45" hidden="1">
       <c r="A55" s="8">
         <v>4</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C55" s="8">
         <v>1</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="10">
@@ -5032,33 +5049,33 @@
         <v>17</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="89.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="89.25" hidden="1" customHeight="1">
       <c r="A56" s="8">
         <v>4</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C56" s="8">
         <v>1</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="10">
@@ -5071,33 +5088,33 @@
         <v>17</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="72" hidden="1">
       <c r="A57" s="8">
         <v>4</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C57" s="8">
         <v>1</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="10">
@@ -5110,33 +5127,33 @@
         <v>17</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M57" s="11" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="86.45" hidden="1">
       <c r="A58" s="8">
         <v>4</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C58" s="8">
         <v>1</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="10">
@@ -5146,33 +5163,33 @@
         <v>46265</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="100.9" hidden="1">
       <c r="A59" s="8">
         <v>4</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C59" s="8">
         <v>1</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="10">
@@ -5185,36 +5202,36 @@
         <v>17</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M59" s="13" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="57.6" hidden="1">
       <c r="A60" s="8">
         <v>4</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C60" s="8">
         <v>1</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H60" s="10">
         <v>45962</v>
@@ -5226,33 +5243,33 @@
         <v>17</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M60" s="11" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="86.45" hidden="1">
       <c r="A61" s="8">
         <v>4</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C61" s="8">
         <v>1</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="10">
@@ -5265,33 +5282,33 @@
         <v>17</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M61" s="11" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="28.9" hidden="1">
       <c r="A62" s="8">
         <v>4</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C62" s="8">
         <v>1</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="10">
@@ -5304,33 +5321,33 @@
         <v>17</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M62" s="11" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="72" hidden="1">
       <c r="A63" s="8">
         <v>4</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C63" s="8">
         <v>2</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="10">
@@ -5340,33 +5357,33 @@
         <v>46203</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L63" s="11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="100.9" hidden="1">
       <c r="A64" s="8">
         <v>4</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C64" s="8">
         <v>2</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="10">
@@ -5379,33 +5396,33 @@
         <v>17</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M64" s="11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="86.45" hidden="1">
       <c r="A65" s="8">
         <v>4</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C65" s="8">
         <v>2</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="10">
@@ -5418,33 +5435,33 @@
         <v>17</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M65" s="11" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="92.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="92.25" hidden="1" customHeight="1">
       <c r="A66" s="8">
         <v>4</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C66" s="8">
         <v>1</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="10">
@@ -5457,31 +5474,31 @@
         <v>17</v>
       </c>
       <c r="K66" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L66" s="12"/>
       <c r="M66" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="100.9" hidden="1">
       <c r="A67" s="8">
         <v>4</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C67" s="8">
         <v>2</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="10">
@@ -5494,33 +5511,33 @@
         <v>17</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L67" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M67" s="11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="115.15" hidden="1">
       <c r="A68" s="8">
         <v>4</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C68" s="8">
         <v>2</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="10">
@@ -5533,33 +5550,33 @@
         <v>17</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L68" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M68" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="86.45" hidden="1">
       <c r="A69" s="8">
         <v>4</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C69" s="8">
         <v>3</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="10">
@@ -5572,36 +5589,36 @@
         <v>17</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L69" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M69" s="11" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="115.15" hidden="1">
       <c r="A70" s="20">
         <v>5</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C70" s="20">
         <v>1</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H70" s="23">
         <v>45931</v>
@@ -5613,36 +5630,36 @@
         <v>17</v>
       </c>
       <c r="K70" s="22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="86.45" hidden="1">
       <c r="A71" s="20">
         <v>5</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C71" s="20">
         <v>1</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H71" s="23">
         <v>45962</v>
@@ -5654,36 +5671,36 @@
         <v>17</v>
       </c>
       <c r="K71" s="22" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="129.6" hidden="1">
       <c r="A72" s="20">
         <v>5</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C72" s="20">
         <v>1</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H72" s="23">
         <v>45931</v>
@@ -5695,36 +5712,36 @@
         <v>17</v>
       </c>
       <c r="K72" s="22" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="72" hidden="1">
       <c r="A73" s="20">
         <v>5</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C73" s="20">
         <v>1</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E73" s="21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H73" s="23">
         <v>45931</v>
@@ -5736,33 +5753,33 @@
         <v>17</v>
       </c>
       <c r="K73" s="22" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="115.15" hidden="1">
       <c r="A74" s="20">
         <v>5</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C74" s="20">
         <v>2</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G74" s="22"/>
       <c r="H74" s="23">
@@ -5775,33 +5792,33 @@
         <v>17</v>
       </c>
       <c r="K74" s="22" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="129.6" hidden="1">
       <c r="A75" s="20">
         <v>5</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C75" s="20">
         <v>2</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G75" s="22"/>
       <c r="H75" s="23">
@@ -5811,32 +5828,32 @@
         <v>46387</v>
       </c>
       <c r="J75" s="22" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="K75" s="22" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L75" s="24"/>
       <c r="M75" s="24"/>
     </row>
-    <row r="76" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:13" ht="100.9" hidden="1">
       <c r="A76" s="20">
         <v>5</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C76" s="20">
         <v>3</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F76" s="22" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G76" s="22"/>
       <c r="H76" s="23">
@@ -5849,33 +5866,33 @@
         <v>17</v>
       </c>
       <c r="K76" s="22" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="28.9" hidden="1">
       <c r="A77" s="20">
         <v>5</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C77" s="20">
         <v>3</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G77" s="22"/>
       <c r="H77" s="23">
@@ -5888,33 +5905,33 @@
         <v>17</v>
       </c>
       <c r="K77" s="22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M77" s="25" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="57.6" hidden="1">
       <c r="A78" s="20">
         <v>5</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C78" s="20">
         <v>4</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G78" s="22"/>
       <c r="H78" s="23">
@@ -5927,33 +5944,33 @@
         <v>17</v>
       </c>
       <c r="K78" s="22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M78" s="25" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="57.6" hidden="1">
       <c r="A79" s="20">
         <v>5</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C79" s="20">
         <v>4</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E79" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G79" s="22"/>
       <c r="H79" s="23">
@@ -5966,33 +5983,33 @@
         <v>17</v>
       </c>
       <c r="K79" s="22" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="57.6" hidden="1">
       <c r="A80" s="20">
         <v>5</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C80" s="20">
         <v>4</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E80" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F80" s="22" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G80" s="22"/>
       <c r="H80" s="23">
@@ -6005,33 +6022,33 @@
         <v>17</v>
       </c>
       <c r="K80" s="22" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="43.15" hidden="1">
       <c r="A81" s="20">
         <v>5</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C81" s="20">
         <v>4</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E81" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F81" s="22" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G81" s="22"/>
       <c r="H81" s="23">
@@ -6041,36 +6058,36 @@
         <v>46112</v>
       </c>
       <c r="J81" s="22" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K81" s="22" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="57.6" hidden="1">
       <c r="A82" s="8">
         <v>6</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C82" s="8">
         <v>1</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H82" s="10">
         <v>45778</v>
@@ -6079,34 +6096,34 @@
         <v>45869</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M82" s="11"/>
     </row>
-    <row r="83" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:13" ht="57.6" hidden="1">
       <c r="A83" s="8">
         <v>6</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C83" s="8">
         <v>1</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H83" s="10">
         <v>45931</v>
@@ -6118,36 +6135,36 @@
         <v>17</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L83" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M83" s="11" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="72" hidden="1">
       <c r="A84" s="8">
         <v>6</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C84" s="8">
         <v>1</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H84" s="10">
         <v>45931</v>
@@ -6159,36 +6176,36 @@
         <v>17</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="115.15" hidden="1">
       <c r="A85" s="8">
         <v>6</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C85" s="8">
         <v>1</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H85" s="10">
         <v>45931</v>
@@ -6197,39 +6214,39 @@
         <v>46203</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L85" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="72" hidden="1">
       <c r="A86" s="8">
         <v>6</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C86" s="8">
         <v>1</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H86" s="10">
         <v>45931</v>
@@ -6238,39 +6255,39 @@
         <v>46387</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L86" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M86" s="11" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="100.9" hidden="1">
       <c r="A87" s="8">
         <v>6</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C87" s="8">
         <v>1</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H87" s="10">
         <v>46023</v>
@@ -6279,39 +6296,39 @@
         <v>46387</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L87" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M87" s="11" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="86.45" hidden="1">
       <c r="A88" s="8">
         <v>6</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C88" s="8">
         <v>1</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H88" s="10">
         <v>46023</v>
@@ -6320,129 +6337,129 @@
         <v>46387</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L88" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M88" s="11" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="28.9" hidden="1">
       <c r="A89" s="8">
         <v>6</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C89" s="8">
         <v>1</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H89" s="10"/>
       <c r="I89" s="10"/>
       <c r="J89" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K89" s="9"/>
       <c r="L89" s="13"/>
     </row>
-    <row r="90" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:13" ht="28.9" hidden="1">
       <c r="A90" s="8">
         <v>6</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C90" s="8">
         <v>1</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E90" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="H90" s="10"/>
       <c r="I90" s="10"/>
       <c r="J90" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K90" s="9"/>
       <c r="L90" s="13"/>
     </row>
-    <row r="91" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:13" ht="28.9" hidden="1">
       <c r="A91" s="8">
         <v>6</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C91" s="8">
         <v>1</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H91" s="10"/>
       <c r="I91" s="10"/>
       <c r="J91" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K91" s="9"/>
       <c r="L91" s="13"/>
     </row>
-    <row r="92" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:13" ht="129.6" hidden="1">
       <c r="A92" s="8">
         <v>6</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C92" s="8">
         <v>2</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H92" s="10">
         <v>46023</v>
@@ -6451,39 +6468,39 @@
         <v>46203</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L92" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M92" s="11" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="115.15" hidden="1">
       <c r="A93" s="8">
         <v>6</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C93" s="8">
         <v>2</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H93" s="10">
         <v>46204</v>
@@ -6492,39 +6509,39 @@
         <v>46387</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L93" s="18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M93" s="18" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="187.15" hidden="1">
       <c r="A94" s="8">
         <v>6</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C94" s="8">
         <v>2</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H94" s="10">
         <v>46023</v>
@@ -6533,37 +6550,37 @@
         <v>46142</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L94" s="18" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M94" s="18"/>
     </row>
-    <row r="95" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:13" ht="129.6" hidden="1">
       <c r="A95" s="8">
         <v>6</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C95" s="8">
         <v>2</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H95" s="10">
         <v>45992</v>
@@ -6572,39 +6589,39 @@
         <v>46142</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L95" s="18" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M95" s="18" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="72" hidden="1">
       <c r="A96" s="8">
         <v>6</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C96" s="8">
         <v>2</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H96" s="10">
         <v>46023</v>
@@ -6613,39 +6630,39 @@
         <v>46387</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L96" s="18" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M96" s="18" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="172.9" hidden="1">
       <c r="A97" s="8">
         <v>6</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C97" s="8">
         <v>2</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H97" s="10">
         <v>46023</v>
@@ -6654,39 +6671,39 @@
         <v>46357</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L97" s="18" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M97" s="18" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="100.9" hidden="1">
       <c r="A98" s="8">
         <v>6</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C98" s="8">
         <v>2</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H98" s="10">
         <v>45931</v>
@@ -6695,37 +6712,37 @@
         <v>46053</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L98" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M98" s="18"/>
     </row>
-    <row r="99" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:13" ht="86.45" hidden="1">
       <c r="A99" s="8">
         <v>6</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C99" s="8">
         <v>2</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H99" s="10">
         <v>45931</v>
@@ -6734,39 +6751,39 @@
         <v>46203</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L99" s="18" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M99" s="18" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="129.6" hidden="1">
       <c r="A100" s="8">
         <v>6</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C100" s="8">
         <v>2</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H100" s="10">
         <v>46023</v>
@@ -6775,39 +6792,39 @@
         <v>46203</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L100" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M100" s="11" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="57.6" hidden="1">
       <c r="A101" s="8">
         <v>6</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C101" s="8">
         <v>2</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H101" s="10">
         <v>46174</v>
@@ -6819,36 +6836,36 @@
         <v>17</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L101" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M101" s="18" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="100.9" hidden="1">
       <c r="A102" s="8">
         <v>6</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C102" s="8">
         <v>2</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H102" s="10">
         <v>46023</v>
@@ -6857,39 +6874,39 @@
         <v>46264</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L102" s="18" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M102" s="18" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="144" hidden="1">
       <c r="A103" s="8">
         <v>6</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C103" s="8">
         <v>2</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H103" s="10">
         <v>46174</v>
@@ -6901,33 +6918,33 @@
         <v>17</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L103" s="18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M103" s="18" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="86.45" hidden="1">
       <c r="A104" s="8">
         <v>6</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C104" s="8">
         <v>3</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G104" s="2"/>
       <c r="H104" s="10">
@@ -6937,36 +6954,36 @@
         <v>46157</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L104" s="18" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M104" s="18" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="86.45" hidden="1">
       <c r="A105" s="8">
         <v>6</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C105" s="8">
         <v>3</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="10">
@@ -6979,36 +6996,36 @@
         <v>17</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L105" s="13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M105" s="18" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="115.15" hidden="1">
       <c r="A106" s="8">
         <v>6</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C106" s="8">
         <v>4</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H106" s="10">
         <v>46023</v>
@@ -7017,36 +7034,36 @@
         <v>46357</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L106" s="18" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M106" s="18" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="57.6" hidden="1">
       <c r="A107" s="8">
         <v>6</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C107" s="8">
         <v>4</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="10">
@@ -7056,34 +7073,34 @@
         <v>46082</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L107" s="18" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M107" s="18"/>
     </row>
-    <row r="108" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:13" ht="57.6" hidden="1">
       <c r="A108" s="8">
         <v>6</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C108" s="8">
         <v>4</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="10">
@@ -7093,34 +7110,34 @@
         <v>46112</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L108" s="18" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M108" s="18"/>
     </row>
-    <row r="109" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:13" ht="158.44999999999999" hidden="1">
       <c r="A109" s="8">
         <v>6</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C109" s="8">
         <v>4</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="10">
@@ -7130,36 +7147,36 @@
         <v>46112</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L109" s="18" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M109" s="18" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="288" hidden="1">
       <c r="A110" s="8">
         <v>6</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C110" s="8">
         <v>5</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G110" s="2"/>
       <c r="H110" s="10">
@@ -7169,34 +7186,34 @@
         <v>46295</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L110" s="18"/>
       <c r="M110" s="18" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="144" hidden="1">
       <c r="A111" s="8">
         <v>6</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C111" s="8">
         <v>5</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G111" s="2"/>
       <c r="H111" s="10">
@@ -7206,17 +7223,24 @@
         <v>46356</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L111" s="18"/>
       <c r="M111" s="18" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M111" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Lojistik"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M111">
     <sortCondition ref="A9:A111"/>
     <sortCondition ref="C9:C111"/>
